--- a/asignaturas/BI/EXCEL/EXAMEN19/Naaira.xlsx
+++ b/asignaturas/BI/EXCEL/EXAMEN19/Naaira.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAW\asignaturas\BI\EXCEL\EXAMEN19\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811F31FB-EDB2-49FD-AEA7-8A4DE5EE0C0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2456D9-9AD8-4B96-918A-2F0515E7A643}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22935" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="560" activeTab="4" xr2:uid="{AE9E8B7B-01CC-4F74-BDA1-D838CC6B9456}"/>
+    <workbookView xWindow="22935" yWindow="-105" windowWidth="23250" windowHeight="12450" tabRatio="560" activeTab="3" xr2:uid="{AE9E8B7B-01CC-4F74-BDA1-D838CC6B9456}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="12" r:id="rId1"/>
@@ -827,9 +827,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -865,48 +862,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
@@ -946,6 +910,42 @@
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2291,21 +2291,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A6C38F7-BC55-4F52-8FFF-6536D1B33BB7}" name="Tabla1" displayName="Tabla1" ref="A3:I98" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A6C38F7-BC55-4F52-8FFF-6536D1B33BB7}" name="Tabla1" displayName="Tabla1" ref="A3:I98" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A3:I98" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState ref="A4:K98">
     <sortCondition ref="I3:I98"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="2" xr3:uid="{1E9847A3-CCEE-4E62-997C-2596EF3E3D3A}" name="Pais" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{2AAD3206-D053-4292-9463-D191DD1E2391}" name="vendedor" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{8B154945-4C11-4516-ABEE-0BCFBF9D0E86}" name="Producto" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{A4B28ED3-CDB0-4E8A-B3D0-31AF2DF7D6B6}" name="Cantidad vendida" dataDxfId="10"/>
-    <tableColumn id="1" xr3:uid="{4756F5B6-9799-4819-AD69-C1EFD8C35F78}" name="PRECIO UNIDAD" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{79F6A9F3-E7A7-44D1-A410-F65B9D0FB5A9}" name="Ingresos" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{D057D720-7C7D-48A3-9561-898B282EA99D}" name="Presupuesto " dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{31EB9F07-C866-4256-9E83-628ACE607237}" name="Fecha" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{73A0B225-E688-4443-BD02-541061CAEEA6}" name="Mes" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{1E9847A3-CCEE-4E62-997C-2596EF3E3D3A}" name="Pais" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{2AAD3206-D053-4292-9463-D191DD1E2391}" name="vendedor" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{8B154945-4C11-4516-ABEE-0BCFBF9D0E86}" name="Producto" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{A4B28ED3-CDB0-4E8A-B3D0-31AF2DF7D6B6}" name="Cantidad vendida" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{4756F5B6-9799-4819-AD69-C1EFD8C35F78}" name="PRECIO UNIDAD" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{79F6A9F3-E7A7-44D1-A410-F65B9D0FB5A9}" name="Ingresos" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{D057D720-7C7D-48A3-9561-898B282EA99D}" name="Presupuesto " dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{31EB9F07-C866-4256-9E83-628ACE607237}" name="Fecha" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{73A0B225-E688-4443-BD02-541061CAEEA6}" name="Mes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5362,7 +5362,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="8" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J8" s="37"/>
+      <c r="J8" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5422,16 +5422,16 @@
         <v>29</v>
       </c>
       <c r="H3" s="6"/>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -5452,14 +5452,14 @@
         <v>44829</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -5480,14 +5480,14 @@
         <v>45351</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -14976,7 +14976,7 @@
     <mergeCell ref="I3:P5"/>
   </mergeCells>
   <conditionalFormatting sqref="M10:N16 L17:P18 M19:N21">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15008,7 +15008,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T32:T39">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15051,19 +15051,19 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="39" t="s">
+      <c r="G4" s="38" t="s">
         <v>4</v>
       </c>
     </row>
@@ -15083,11 +15083,11 @@
       <c r="G5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="44"/>
-      <c r="J5" s="45">
+      <c r="I5" s="43"/>
+      <c r="J5" s="44">
         <v>0.25</v>
       </c>
-      <c r="K5" s="42" t="s">
+      <c r="K5" s="41" t="s">
         <v>111</v>
       </c>
     </row>
@@ -15107,9 +15107,9 @@
       <c r="G6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C7" s="10" t="s">
@@ -15127,9 +15127,9 @@
       <c r="G7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C8" s="10" t="s">
@@ -15147,11 +15147,11 @@
       <c r="G8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="44"/>
-      <c r="J8" s="45">
+      <c r="I8" s="43"/>
+      <c r="J8" s="44">
         <v>0.25</v>
       </c>
-      <c r="K8" s="42" t="s">
+      <c r="K8" s="41" t="s">
         <v>112</v>
       </c>
     </row>
@@ -15171,9 +15171,9 @@
       <c r="G9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C10" s="10" t="s">
@@ -15191,9 +15191,9 @@
       <c r="G10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C11" s="10" t="s">
@@ -15211,11 +15211,11 @@
       <c r="G11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="44"/>
-      <c r="J11" s="45">
+      <c r="I11" s="43"/>
+      <c r="J11" s="44">
         <v>0.25</v>
       </c>
-      <c r="K11" s="43" t="s">
+      <c r="K11" s="42" t="s">
         <v>54</v>
       </c>
     </row>
@@ -15235,29 +15235,29 @@
       <c r="G12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="40" t="s">
+      <c r="E13" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="40">
         <v>8826</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
     </row>
     <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="C14" s="10" t="s">
@@ -15275,11 +15275,11 @@
       <c r="G14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="44"/>
-      <c r="J14" s="45">
+      <c r="I14" s="43"/>
+      <c r="J14" s="44">
         <v>0.25</v>
       </c>
-      <c r="K14" s="42" t="s">
+      <c r="K14" s="41" t="s">
         <v>55</v>
       </c>
     </row>
@@ -15299,8 +15299,8 @@
       <c r="G15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C16" s="10" t="s">
@@ -15318,26 +15318,26 @@
       <c r="G16" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <f>SUM(I5,I8,I11,I14)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="43"/>
+      <c r="J16" s="42"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <conditionalFormatting sqref="E5:E16">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="13" priority="3">
       <formula>IF(E5="MADRID",G5="SUR")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C16">
-    <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="M">
+    <cfRule type="beginsWith" dxfId="12" priority="2" operator="beginsWith" text="M">
       <formula>LEFT(C5,LEN("M"))="M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G16">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>$G$5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15353,7 +15353,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -15434,11 +15435,11 @@
         <f>FIND(",",B5)</f>
         <v>6</v>
       </c>
-      <c r="E5" s="46" t="str">
+      <c r="E5" s="45" t="str">
         <f>RIGHT(B5,C5-D15+11-D5+13)</f>
         <v>LOPEZ, GONZALEZ, SARA ALEJANDRA,666666661</v>
       </c>
-      <c r="F5" s="46"/>
+      <c r="F5" s="45"/>
       <c r="G5" s="10" t="str">
         <f>RIGHT(B5,C5-D15-10-D5-8)</f>
         <v>666666661</v>
@@ -15466,7 +15467,7 @@
         <f t="shared" ref="D6:D18" si="0">FIND(",",B6)</f>
         <v>6</v>
       </c>
-      <c r="E6" s="46" t="str">
+      <c r="E6" s="45" t="str">
         <f t="shared" ref="E6:E18" si="1">RIGHT(B6,C6-D16+11-D6+13)</f>
         <v>AHMED, MONNE, MARCOS,666666662</v>
       </c>
@@ -15491,14 +15492,14 @@
         <v>132</v>
       </c>
       <c r="C7" s="10">
-        <f t="shared" ref="C6:C18" si="2">LEN(B7)</f>
+        <f t="shared" ref="C7:C18" si="2">LEN(B7)</f>
         <v>33</v>
       </c>
       <c r="D7" s="10">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E7" s="46" t="str">
+      <c r="E7" s="45" t="str">
         <f t="shared" si="1"/>
         <v>GARCIA, SERRANO, MARCOS,666666663</v>
       </c>
@@ -15530,7 +15531,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E8" s="46" t="str">
+      <c r="E8" s="45" t="str">
         <f t="shared" si="1"/>
         <v>GARCIA, LAPEÑA, DANIEL,666666664</v>
       </c>
@@ -15556,7 +15557,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E9" s="46" t="str">
+      <c r="E9" s="45" t="str">
         <f t="shared" si="1"/>
         <v>CONDE, MORALES, ALEJANDRO,666666665</v>
       </c>
@@ -15578,7 +15579,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E10" s="46" t="str">
+      <c r="E10" s="45" t="str">
         <f t="shared" si="1"/>
         <v>LABRADA, ORTEGA, LUIS MIGUEL,666666666</v>
       </c>
@@ -15600,7 +15601,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E11" s="46" t="str">
+      <c r="E11" s="45" t="str">
         <f t="shared" si="1"/>
         <v>BELTRE, CARMONA, LUIS ANGEL,666666667</v>
       </c>
@@ -15622,7 +15623,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E12" s="46" t="str">
+      <c r="E12" s="45" t="str">
         <f t="shared" si="1"/>
         <v>MUÑOZ, ZORRO, ROBERTO,666666668</v>
       </c>
@@ -15644,7 +15645,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E13" s="46" t="str">
+      <c r="E13" s="45" t="str">
         <f t="shared" si="1"/>
         <v>TEXEIRA, BARBA, JOSE ANTONIO,666666669</v>
       </c>
@@ -15666,7 +15667,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E14" s="46" t="str">
+      <c r="E14" s="45" t="str">
         <f t="shared" si="1"/>
         <v>CARDENAS, RODRIGUEZ, NICOLAS,666666670</v>
       </c>
@@ -15688,7 +15689,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E15" s="46" t="str">
+      <c r="E15" s="45" t="str">
         <f t="shared" si="1"/>
         <v>SOBRINO, ARRIBAS, CESAR,666666671</v>
       </c>
@@ -15710,7 +15711,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E16" s="46" t="str">
+      <c r="E16" s="45" t="str">
         <f t="shared" si="1"/>
         <v>TORRES, MARTINEZ, MARIA,666666672</v>
       </c>
@@ -15732,7 +15733,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E17" s="46" t="str">
+      <c r="E17" s="45" t="str">
         <f t="shared" si="1"/>
         <v>NAVARRO, VALLEJO, MARIO,666666673</v>
       </c>
@@ -15754,13 +15755,13 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E18" s="46" t="str">
+      <c r="E18" s="45" t="str">
         <f t="shared" si="1"/>
         <v>OCHOVO, QUERO, ALEJANDRO,666666674</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10" t="str">
-        <f t="shared" ref="G6:G18" si="3">RIGHT(B18,C18-D28-10-D18-8)</f>
+        <f t="shared" ref="G18" si="3">RIGHT(B18,C18-D28-10-D18-8)</f>
         <v>666666674</v>
       </c>
     </row>
@@ -15825,7 +15826,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="37" t="s">
         <v>60</v>
       </c>
     </row>
